--- a/src/instructions/et_task_instructions.xlsx
+++ b/src/instructions/et_task_instructions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akoun\Desktop\Biocruces\begibraintool\src\instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03B5F1D-153F-4D73-A737-05D0ABA1C6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA240A72-49EB-446C-A17B-9488297E7A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -122,7 +122,7 @@
     <t>Mira al estímulo que aparece en el centro de la pantalla durante 60 segundos, manten la mirada lo más fija posible.</t>
   </si>
   <si>
-    <t>Pulsa la barra espaciadora cuando quieras empezar.</t>
+    <t>Pulsa el botón central para empezar.</t>
   </si>
 </sst>
 </file>
@@ -566,12 +566,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -689,15 +686,25 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -719,16 +726,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>